--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -723,22 +723,22 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -771,12 +771,12 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +937,903 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +804,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -975,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1002,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1041,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1084,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1117,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1141,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1228,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1252,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1306,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1339,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1363,17 +1399,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1383,13 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1500,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1611,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1722,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1730,22 +1770,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1778,12 +1818,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1827,13 +1867,810 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>—/9</t>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1110,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1229,24 +1229,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1348,24 +1348,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1568,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1629,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1712,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1736,33 +1748,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1790,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1823,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1847,17 +1867,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1867,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1977,7 +1997,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1992,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2103,7 +2123,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2203,7 +2223,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2218,7 +2238,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2329,7 +2349,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2439,12 +2459,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2555,7 +2575,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2636,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2665,12 +2685,920 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1816,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1925,32 +1925,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,17 +1986,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2002,12 +2006,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2184,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2238,7 +2242,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2338,7 +2342,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,32 +2381,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2410,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2434,17 +2442,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2454,12 +2462,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2492,32 +2500,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2525,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2549,33 +2561,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2619,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2636,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2660,37 +2680,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2718,32 +2738,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2751,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2775,17 +2799,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2795,13 +2819,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2901,7 +2929,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3027,7 +3055,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3142,7 +3170,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3242,7 +3270,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3314,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3358,12 +3386,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3429,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3483,7 +3511,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3572,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3598,7 +3626,796 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,13 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2188,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2232,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,18 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2537,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2656,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2710,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,14 +2826,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -2829,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2869,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2890,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2914,17 +2930,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2934,13 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3083,32 +3103,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3116,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,17 +3164,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3160,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3198,32 +3222,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3231,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3255,17 +3283,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3275,13 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3309,32 +3341,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3342,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3366,32 +3402,32 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3424,32 +3460,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3457,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3481,17 +3521,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3501,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3611,7 +3651,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3654,32 +3694,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3687,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3711,33 +3755,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3837,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3913,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3967,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4067,7 +4115,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4139,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4183,13 +4231,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4365,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4409,13 +4461,703 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr"/>
-      <c r="AC34" s="2" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>84.5</t>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,13 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,14 +2473,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>84.5</t>
@@ -2484,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2841,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3421,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3432,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3708,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3780,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3813,32 +3817,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3846,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,17 +3878,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3890,17 +3898,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3928,32 +3936,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3961,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,17 +3997,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4005,17 +4017,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4043,32 +4055,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -4076,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4100,17 +4116,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4120,13 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4154,32 +4174,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4187,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,37 +4235,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4293,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4302,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4326,37 +4354,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4384,32 +4412,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4417,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4441,17 +4473,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4461,17 +4493,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4499,32 +4531,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4532,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4556,17 +4592,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4576,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4686,7 +4722,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4701,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4806,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4916,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4931,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5036,13 +5072,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5152,12 +5192,698 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4422,24 +4422,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4541,24 +4541,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4650,32 +4650,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4683,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4707,17 +4711,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4727,17 +4731,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4769,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4798,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4822,17 +4830,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4842,17 +4850,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4880,32 +4888,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4913,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,17 +4949,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4957,12 +4969,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -4995,32 +5007,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5028,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5052,17 +5068,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5072,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5110,32 +5126,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5143,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5167,37 +5187,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5373,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5412,7 +5432,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5488,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,17 +5552,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5642,7 +5662,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5714,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5758,12 +5778,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5829,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5883,7 +5903,578 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4374,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5136,24 +5136,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5245,32 +5245,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5278,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,17 +5306,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5322,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5360,32 +5364,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5393,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,17 +5425,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5437,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5475,32 +5483,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5508,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,17 +5544,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5552,12 +5564,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5590,32 +5602,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -5623,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,17 +5663,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5667,13 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5788,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5888,7 +5908,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5903,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6013,12 +6033,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6133,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,17 +6258,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6363,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6371,22 +6391,22 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6419,12 +6439,12 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6463,18 +6483,367 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5493,24 +5493,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5721,32 +5721,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,32 +5782,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5836,32 +5840,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5869,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,17 +5901,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5913,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6038,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6138,7 +6146,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6214,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6268,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6444,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6498,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6608,7 +6616,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6674,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6789,7 +6797,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6833,17 +6841,247 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>11/15</t>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,14 +2592,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>75.7</t>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,14 +2711,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,14 +4012,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,14 +4369,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>75.7</t>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,17 +4607,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>75.7</t>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5850,24 +5850,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5959,32 +5959,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5992,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,37 +6020,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6074,32 +6078,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6107,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,17 +6139,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6151,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6197,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6222,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,37 +6258,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6304,32 +6316,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6337,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6361,37 +6377,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6419,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6452,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,32 +6496,32 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6534,32 +6554,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -6567,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6591,17 +6615,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6611,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6736,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6846,7 +6870,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6912,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6974,22 +6998,22 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7022,12 +7046,12 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7041,47 +7065,737 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
         <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr">
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X56" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z56" s="2" t="inlineStr">
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>15/15</t>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,14 +942,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>84.2</t>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>84.2</t>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,14 +3893,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>84.2</t>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,14 +4726,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>84.2</t>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,22 +5321,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,14 +5559,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6445,24 +6445,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6564,24 +6564,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,22 +6630,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6673,32 +6673,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -6706,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6730,37 +6734,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6788,32 +6792,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6821,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,17 +6853,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6865,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6903,32 +6911,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6936,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6960,37 +6972,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7018,32 +7030,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7051,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,37 +7091,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7149,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7166,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7190,17 +7210,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7210,12 +7230,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7281,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7320,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7363,32 +7383,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7396,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7420,17 +7444,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7440,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7565,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7675,12 +7699,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7799,6 +7823,926 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,14 +4250,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,14 +5440,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6273,14 +6273,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6392,14 +6392,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,22 +6511,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7040,24 +7040,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7159,24 +7159,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7268,32 +7268,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -7301,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7325,17 +7329,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7345,12 +7349,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7405,12 +7409,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7420,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,14 +7463,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -7474,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7502,32 +7506,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7535,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,37 +7567,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7617,32 +7625,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7650,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,37 +7686,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7744,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7765,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,29 +7805,29 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>81.8</t>
@@ -7819,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7919,7 +7935,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7934,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7962,32 +7978,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7995,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,17 +8039,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8039,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8225,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8340,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8394,7 +8414,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8570,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8619,7 +8639,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8632,22 +8652,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8680,12 +8700,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8699,45 +8719,850 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="V70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr">
+      <c r="W71" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X70" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="Y71" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z70" s="2" t="inlineStr">
+      <c r="Z71" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>81.7</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr">
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
         <is>
           <t>9/15</t>
         </is>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,17 +1533,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,17 +3302,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4845,22 +4845,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,17 +5797,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,22 +5916,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,22 +6868,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6987,17 +6987,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7106,17 +7106,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7988,24 +7988,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8212,32 +8212,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8245,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8269,37 +8273,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8327,32 +8331,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8360,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8384,32 +8392,32 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8442,32 +8450,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8475,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8499,32 +8511,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8557,32 +8569,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -8590,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8614,32 +8630,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8672,32 +8688,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8705,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8729,37 +8749,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8859,7 +8879,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8874,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8974,7 +8994,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9050,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9165,7 +9185,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9219,7 +9239,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9334,7 +9354,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9434,7 +9454,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9449,7 +9469,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9457,22 +9477,22 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9505,12 +9525,12 @@
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9524,47 +9544,1197 @@
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr">
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X77" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z77" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>82.8</t>
         </is>
       </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>9/15</t>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4845,22 +4845,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,17 +7230,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7820,22 +7820,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,22 +8288,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8526,22 +8526,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8807,32 +8807,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -8840,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,17 +8868,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8884,12 +8888,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8922,32 +8926,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8955,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8979,17 +8987,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8999,17 +9007,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -9037,32 +9045,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9070,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9094,37 +9106,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9152,32 +9164,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9185,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9209,37 +9225,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9267,32 +9283,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9300,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9324,17 +9344,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9344,17 +9364,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9382,32 +9402,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9415,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9439,17 +9463,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9459,12 +9483,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9497,32 +9521,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -9530,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9554,17 +9582,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9574,12 +9602,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9645,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9684,7 +9712,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9699,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9727,32 +9755,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9760,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9784,37 +9816,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9842,32 +9874,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9875,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9899,37 +9935,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9990,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10105,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10144,7 +10180,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10159,7 +10195,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10335,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10374,7 +10410,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10450,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10494,17 +10530,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10609,12 +10645,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10680,7 +10716,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10724,17 +10760,822 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>80.5</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>5/15</t>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6873,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8769,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9884,24 +9884,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10108,32 +10108,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10141,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10165,17 +10169,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10185,17 +10189,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10223,32 +10227,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10256,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10280,17 +10288,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10300,17 +10308,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10338,32 +10346,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10371,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10395,17 +10407,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10415,12 +10427,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10486,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10601,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10655,7 +10667,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10728,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10770,7 +10782,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10946,7 +10958,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11061,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11115,7 +11127,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11188,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11230,7 +11242,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11303,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11340,7 +11352,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11353,22 +11365,22 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11401,12 +11413,12 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11420,7 +11432,7 @@
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
@@ -11445,7 +11457,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11455,12 +11467,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11468,22 +11480,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11516,12 +11528,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11535,45 +11547,275 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
         <is>
           <t>2/15</t>
         </is>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC96"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,17 +4017,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,17 +7230,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,17 +7468,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,17 +7587,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,17 +9007,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,17 +9126,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,17 +9483,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10356,24 +10356,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10465,32 +10465,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10498,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10522,17 +10526,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10542,17 +10546,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10580,32 +10584,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -10613,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10637,17 +10645,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10657,12 +10665,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10695,32 +10703,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10728,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10752,17 +10764,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10772,17 +10784,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10822,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10843,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10867,17 +10883,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10887,17 +10903,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11012,7 +11028,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11089,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11155,32 +11171,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11188,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11212,17 +11232,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11232,12 +11252,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11303,7 +11323,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11357,7 +11377,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11457,7 +11477,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11472,7 +11492,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11553,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11572,7 +11592,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11648,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11763,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11812,12 +11832,242 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
           <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-浦东78路.xlsx
+++ b/data/export/2026-09-25-浦东78路.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,17 +7825,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9364,17 +9364,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,17 +10189,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10713,24 +10713,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10832,24 +10832,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10941,32 +10941,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -10974,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10998,17 +11002,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11018,17 +11022,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11181,24 +11185,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11208,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11257,12 +11261,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11405,32 +11409,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11438,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11462,17 +11470,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11482,17 +11490,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11520,32 +11528,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -11553,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11577,17 +11589,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11597,12 +11609,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11635,32 +11647,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -11668,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11692,17 +11708,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11712,17 +11728,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -11750,32 +11766,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -11783,7 +11803,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11807,17 +11827,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11827,12 +11847,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11898,7 +11918,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11942,17 +11962,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12033,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12057,12 +12077,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
